--- a/IngSoftware/propuesta/Riesgos/TemplateRiesgos.xlsx
+++ b/IngSoftware/propuesta/Riesgos/TemplateRiesgos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\OneDrive\Desktop\sape\propuesta\Riesgos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\repos\TrabajoFinalAUS\IngSoftware\propuesta\Riesgos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4D2C47-799C-4650-A27C-5BB9CAD9D1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E7B1DB-B7CD-45C4-9E60-B3BC5956C22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -138,9 +138,6 @@
 3. Los objetivos de los desarrolladores no son claros.</t>
   </si>
   <si>
-    <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el recursos destinados al proyecto.</t>
-  </si>
-  <si>
     <t>Dado que los repositorios de codigo ofrecidos por compañías (como Github, de Microsoft) pueden ser inaccesibes (por caídas de sus servicios, falta de acceso a la internet), existe la posibilidad de que los desarrolladores no puedan colaborar realizando revisiones de codigo (Pull Requests)</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
 Si el cliente aún así no quiere extender el cronograma, avisarle que el producto no poseerá determinados estándares de calidad.</t>
   </si>
   <si>
-    <t>Dado que el cronograma puede llegar a ser muy corto, porque fue acelerado(por el cliente) o mal planeado desde un principio, existe la posibilidad de que el equipo sufra gran presión y se vea afectado su bienestar.</t>
-  </si>
-  <si>
     <t>1. Realizar sugerencias al cliente sobre tiempos ideales para obtener un producto de calidad, y que riesgos se corren si estos estándares no se cumplen.
 2. Dejar por contrato que se va a cargar una tarifa por cada vez que se quiera realizar una modificación que achique el cronograma.</t>
   </si>
@@ -301,6 +295,12 @@
 Subcondición 2: Los Desarrolladores estimaron menos tiempo del que realmente les iba a costar cada funcionalidad.
 Subcondición 3: Error durante el armado del cronograma por parte del Gerente del Proyecto.
 Subcondición 3: El cliente puede tardar mucho tiempo en responder, pero pedir cambios de manera muy acelerada.</t>
+  </si>
+  <si>
+    <t>Dado que existe rotación de personal y se destinan recursos para capacitar gente nueva entonces hay preocupación por perder el recursos destinado al proyecto.</t>
+  </si>
+  <si>
+    <t>Dado que el cronograma puede llegar a ser muy corto, porque fue acelerado(por el cliente o mal planeado desde un principio), existe la posibilidad de que el equipo sufra gran presión y se vea afectado su bienestar.</t>
   </si>
 </sst>
 </file>
@@ -310,7 +310,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -359,6 +359,14 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -418,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -487,11 +495,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -780,20 +791,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
       <c r="N1" s="1"/>
       <c r="O1" t="s">
         <v>6</v>
@@ -838,15 +849,15 @@
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="120" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>13</v>
@@ -860,18 +871,18 @@
       <c r="F3" s="3">
         <v>0.8</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="28">
         <f t="shared" ref="G3:G11" si="0">E3*F3</f>
         <v>12000</v>
       </c>
       <c r="H3" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K3" s="17" t="s">
         <v>20</v>
@@ -883,7 +894,7 @@
       <c r="M3" s="12"/>
       <c r="N3" s="1"/>
       <c r="O3" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="81.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -891,10 +902,10 @@
         <v>26</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>14</v>
@@ -910,7 +921,7 @@
         <v>17500</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>25</v>
@@ -928,7 +939,7 @@
       <c r="M4" s="12"/>
       <c r="N4" s="1"/>
       <c r="O4" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -936,7 +947,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" s="14" t="s">
         <v>23</v>
@@ -955,7 +966,7 @@
         <v>21600</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>28</v>
@@ -972,7 +983,7 @@
       </c>
       <c r="M5" s="12"/>
       <c r="O5" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
@@ -980,7 +991,7 @@
         <v>22</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C6" s="14" t="s">
         <v>13</v>
@@ -999,13 +1010,13 @@
         <v>18000</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K6" s="17" t="s">
         <v>24</v>
@@ -1017,13 +1028,13 @@
     </row>
     <row r="7" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="13">
         <v>45728</v>
@@ -1039,13 +1050,13 @@
         <v>10500</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K7" s="17" t="s">
         <v>24</v>
@@ -1054,13 +1065,13 @@
     </row>
     <row r="8" spans="1:15" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>46</v>
       </c>
       <c r="D8" s="13">
         <v>45728</v>
@@ -1076,13 +1087,13 @@
         <v>10000</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K8" s="17" t="s">
         <v>24</v>
@@ -1091,10 +1102,10 @@
     </row>
     <row r="9" spans="1:15" ht="102" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="14" t="s">
         <v>13</v>
@@ -1113,13 +1124,13 @@
         <v>700</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K9" s="17" t="s">
         <v>24</v>
@@ -1128,13 +1139,13 @@
     </row>
     <row r="10" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" s="13">
         <v>45728</v>
@@ -1150,13 +1161,13 @@
         <v>2000</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K10" s="17" t="s">
         <v>24</v>
@@ -1165,13 +1176,13 @@
     </row>
     <row r="11" spans="1:15" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" s="13">
         <v>45728</v>
@@ -1187,13 +1198,13 @@
         <v>2000</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>28</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K11" s="17" t="s">
         <v>24</v>
@@ -6178,12 +6189,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="23" t="s">
@@ -6207,24 +6218,24 @@
         <v>31</v>
       </c>
       <c r="C3" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="339.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C4" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="216.75" x14ac:dyDescent="0.2">
@@ -6232,13 +6243,13 @@
         <v>22</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>61</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="140.25" x14ac:dyDescent="0.2">
@@ -6246,13 +6257,13 @@
         <v>27</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
